--- a/output/yearly_benthic_cover_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_89_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.43093086454636</v>
+        <v>45.24937863376399</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1046119795605</v>
+        <v>99.16034707666788</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00656907959093</v>
+        <v>87.90277871229796</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92106846094151</v>
+        <v>45.82539387467031</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228683178228427</v>
+        <v>2.228489189773821</v>
       </c>
       <c r="E3" t="n">
-        <v>5.700853222753829</v>
+        <v>5.640726920586574</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428943927428091</v>
+        <v>0.7428297299246071</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97069954176507</v>
+        <v>33.93853535422761</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17314206616922</v>
+        <v>34.17016757653192</v>
       </c>
       <c r="I3" t="n">
-        <v>6.547206723289018</v>
+        <v>6.539344129224647</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643089954642557</v>
+        <v>4.642685812028794</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99343092040907</v>
+        <v>12.09722128770204</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85048446966073</v>
+        <v>48.84263048802675</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7649838510113</v>
+        <v>106.7652456503991</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05083794851566</v>
+        <v>86.94956574019136</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59673347153831</v>
+        <v>42.5056104625761</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182407110767501</v>
+        <v>2.182238804785277</v>
       </c>
       <c r="E4" t="n">
-        <v>6.493719527685943</v>
+        <v>6.433802106570004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444496991304846</v>
+        <v>0.7443848423648421</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26533666244402</v>
+        <v>33.23417011284197</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2446861600023</v>
+        <v>34.24170274878274</v>
       </c>
       <c r="I4" t="n">
-        <v>5.467428168919881</v>
+        <v>5.460861860066278</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652810619565529</v>
+        <v>4.652405264780263</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94916205148436</v>
+        <v>13.05043425980864</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27223762355262</v>
+        <v>44.26230682958126</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81813314657529</v>
+        <v>99.818351551966</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.75567313825617</v>
+        <v>85.77766759028114</v>
       </c>
       <c r="C5" t="n">
-        <v>42.15011321322957</v>
+        <v>42.18115075277218</v>
       </c>
       <c r="D5" t="n">
-        <v>2.118766060201156</v>
+        <v>2.124888996304329</v>
       </c>
       <c r="E5" t="n">
-        <v>7.065068781339312</v>
+        <v>7.024516771547082</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745770456065022</v>
+        <v>0.7457035565299261</v>
       </c>
       <c r="G5" t="n">
-        <v>32.29528805776523</v>
+        <v>32.36076740053787</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30544097899102</v>
+        <v>34.30236360037659</v>
       </c>
       <c r="I5" t="n">
-        <v>4.564273453488053</v>
+        <v>4.558780036673299</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661065350406387</v>
+        <v>4.660647228312038</v>
       </c>
       <c r="K5" t="n">
-        <v>14.24432686174383</v>
+        <v>14.22233240971886</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45368692033439</v>
+        <v>43.4448262302849</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84812699530779</v>
+        <v>99.84830939277595</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.16169881292534</v>
+        <v>84.28551343844909</v>
       </c>
       <c r="C6" t="n">
-        <v>41.26484589857989</v>
+        <v>41.39688646706956</v>
       </c>
       <c r="D6" t="n">
-        <v>2.040419161772485</v>
+        <v>2.051588588848838</v>
       </c>
       <c r="E6" t="n">
-        <v>7.438702733754532</v>
+        <v>7.416314866209291</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468956168119415</v>
+        <v>0.7468256070227755</v>
       </c>
       <c r="G6" t="n">
-        <v>31.10108559213475</v>
+        <v>31.24444676442118</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35719837334931</v>
+        <v>34.35397792304767</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80929973002768</v>
+        <v>3.804699645007007</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668097605074633</v>
+        <v>4.667660043892346</v>
       </c>
       <c r="K6" t="n">
-        <v>15.83830118707467</v>
+        <v>15.71448656155091</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77006754063745</v>
+        <v>42.76199419258305</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87321462629201</v>
+        <v>99.87336722120351</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.2863306417054</v>
+        <v>82.68115109091207</v>
       </c>
       <c r="C7" t="n">
-        <v>39.9808043402021</v>
+        <v>40.38324398521604</v>
       </c>
       <c r="D7" t="n">
-        <v>1.948629296209166</v>
+        <v>1.973263393138086</v>
       </c>
       <c r="E7" t="n">
-        <v>7.633817448743324</v>
+        <v>7.662282905026018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478573036852217</v>
+        <v>0.7477814488909371</v>
       </c>
       <c r="G7" t="n">
-        <v>29.7019787228896</v>
+        <v>30.05160165843888</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4014359695202</v>
+        <v>34.3979466489831</v>
       </c>
       <c r="I7" t="n">
-        <v>3.178503752625267</v>
+        <v>3.17464098086669</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674108148032635</v>
+        <v>4.673634055568357</v>
       </c>
       <c r="K7" t="n">
-        <v>17.71366935829456</v>
+        <v>17.31884890908792</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19971242011368</v>
+        <v>42.19222100444585</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89418611861035</v>
+        <v>99.89431389874981</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.2267047033118</v>
+        <v>87.61450041566268</v>
       </c>
       <c r="C8" t="n">
-        <v>42.34768631695482</v>
+        <v>42.71609136657656</v>
       </c>
       <c r="D8" t="n">
-        <v>1.952820504360459</v>
+        <v>1.977505799910029</v>
       </c>
       <c r="E8" t="n">
-        <v>9.509844902615461</v>
+        <v>9.516744464727742</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494658321176471</v>
+        <v>0.7493891375014593</v>
       </c>
       <c r="G8" t="n">
-        <v>30.22663857353962</v>
+        <v>30.56428918997685</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47542827741177</v>
+        <v>34.47190032506712</v>
       </c>
       <c r="I8" t="n">
-        <v>5.628345162531564</v>
+        <v>5.650989389095344</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684161450735292</v>
+        <v>4.683682109384121</v>
       </c>
       <c r="K8" t="n">
-        <v>12.7732952966882</v>
+        <v>12.38549958433735</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69180953897619</v>
+        <v>44.71044684442368</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81279115261921</v>
+        <v>99.81203779533757</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.04289029185372</v>
+        <v>85.63033520427932</v>
       </c>
       <c r="C9" t="n">
-        <v>41.03667000708227</v>
+        <v>41.60862301810712</v>
       </c>
       <c r="D9" t="n">
-        <v>1.853934013051414</v>
+        <v>1.887674804981699</v>
       </c>
       <c r="E9" t="n">
-        <v>9.811441844501106</v>
+        <v>9.870733934430625</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508461883831372</v>
+        <v>0.7507653914925577</v>
       </c>
       <c r="G9" t="n">
-        <v>28.69602875767082</v>
+        <v>29.17586317001891</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53892466562431</v>
+        <v>34.53520800865765</v>
       </c>
       <c r="I9" t="n">
-        <v>4.698926145228321</v>
+        <v>4.717806197869389</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692788677394606</v>
+        <v>4.692283696828486</v>
       </c>
       <c r="K9" t="n">
-        <v>14.95710970814628</v>
+        <v>14.36966479572066</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84987736359002</v>
+        <v>43.86474025869736</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84365707881858</v>
+        <v>99.84302807252516</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.70750838190139</v>
+        <v>83.43905719194689</v>
       </c>
       <c r="C10" t="n">
-        <v>39.42949752493583</v>
+        <v>40.14901014940652</v>
       </c>
       <c r="D10" t="n">
-        <v>1.749422998349069</v>
+        <v>1.789435012492847</v>
       </c>
       <c r="E10" t="n">
-        <v>9.91200591846383</v>
+        <v>10.01331539520456</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520330172171988</v>
+        <v>0.7519464056270792</v>
       </c>
       <c r="G10" t="n">
-        <v>27.07836002605526</v>
+        <v>27.6574709469826</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59351879199115</v>
+        <v>34.58953465884563</v>
       </c>
       <c r="I10" t="n">
-        <v>3.921961272217376</v>
+        <v>3.937689737624924</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700206357607492</v>
+        <v>4.699665035169245</v>
       </c>
       <c r="K10" t="n">
-        <v>17.29249161809864</v>
+        <v>16.56094280805312</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14748513070919</v>
+        <v>43.15899687037729</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86947427374365</v>
+        <v>99.86894982783693</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.19768129601438</v>
+        <v>81.01196086653073</v>
       </c>
       <c r="C11" t="n">
-        <v>37.52671171756193</v>
+        <v>38.33197278733883</v>
       </c>
       <c r="D11" t="n">
-        <v>1.638309011622603</v>
+        <v>1.681641995233472</v>
       </c>
       <c r="E11" t="n">
-        <v>9.827906159702303</v>
+        <v>9.957768296242506</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530559951335575</v>
+        <v>0.7529630369957599</v>
       </c>
       <c r="G11" t="n">
-        <v>25.35848750846004</v>
+        <v>25.99142427732145</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64057577614365</v>
+        <v>34.63629970180494</v>
       </c>
       <c r="I11" t="n">
-        <v>3.272746875367492</v>
+        <v>3.285844577709097</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706599969584733</v>
+        <v>4.7060189812235</v>
       </c>
       <c r="K11" t="n">
-        <v>19.8023187039856</v>
+        <v>18.98803913346927</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56202620977979</v>
+        <v>42.57060780870231</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89105663132733</v>
+        <v>99.89061972951042</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.72600892111085</v>
+        <v>78.48416452613336</v>
       </c>
       <c r="C12" t="n">
-        <v>35.56063447714932</v>
+        <v>36.31236856785541</v>
       </c>
       <c r="D12" t="n">
-        <v>1.530135456945587</v>
+        <v>1.570506577429329</v>
       </c>
       <c r="E12" t="n">
-        <v>9.63407389420585</v>
+        <v>9.75658351614141</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539378133653049</v>
+        <v>0.7538397177900882</v>
       </c>
       <c r="G12" t="n">
-        <v>23.68412832740054</v>
+        <v>24.27371753321518</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68113941480403</v>
+        <v>34.67662701834404</v>
       </c>
       <c r="I12" t="n">
-        <v>2.730482680856387</v>
+        <v>2.741391927025259</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712111333533154</v>
+        <v>4.711498236188052</v>
       </c>
       <c r="K12" t="n">
-        <v>22.27399107888916</v>
+        <v>21.51583547386665</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07446480853463</v>
+        <v>42.08052249778603</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9090903645731</v>
+        <v>99.90872653950808</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.15194533515951</v>
+        <v>75.97053115965512</v>
       </c>
       <c r="C13" t="n">
-        <v>33.40744561164043</v>
+        <v>34.22176285685129</v>
       </c>
       <c r="D13" t="n">
-        <v>1.418544049972027</v>
+        <v>1.461083800085499</v>
       </c>
       <c r="E13" t="n">
-        <v>9.311086355044342</v>
+        <v>9.457938560957661</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546994902136366</v>
+        <v>0.7545960942756057</v>
       </c>
       <c r="G13" t="n">
-        <v>21.95686608339454</v>
+        <v>22.58248132502836</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71617654982729</v>
+        <v>34.71142033667785</v>
       </c>
       <c r="I13" t="n">
-        <v>2.277700992872442</v>
+        <v>2.286785453407622</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716871813835228</v>
+        <v>4.716225589222537</v>
       </c>
       <c r="K13" t="n">
-        <v>24.84805466484051</v>
+        <v>24.02946884034487</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66865298238417</v>
+        <v>41.67261852705314</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92415325886509</v>
+        <v>99.92385022424929</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.49967958336171</v>
+        <v>82.93817719546355</v>
       </c>
       <c r="C14" t="n">
-        <v>38.06905128341035</v>
+        <v>38.61882585410319</v>
       </c>
       <c r="D14" t="n">
-        <v>1.420164993653465</v>
+        <v>1.462761051618435</v>
       </c>
       <c r="E14" t="n">
-        <v>11.87397478441291</v>
+        <v>11.89068519303114</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555618711668893</v>
+        <v>0.7554623330606757</v>
       </c>
       <c r="G14" t="n">
-        <v>24.06285042510239</v>
+        <v>24.5542497676985</v>
       </c>
       <c r="H14" t="n">
-        <v>36.83674071630721</v>
+        <v>36.69711219807933</v>
       </c>
       <c r="I14" t="n">
-        <v>2.828125097925787</v>
+        <v>2.856267070346251</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722261694793057</v>
+        <v>4.721639581629224</v>
       </c>
       <c r="K14" t="n">
-        <v>17.50032041663828</v>
+        <v>17.06182280453644</v>
       </c>
       <c r="L14" t="n">
-        <v>44.33646506191995</v>
+        <v>44.22425160877854</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90583676196857</v>
+        <v>99.90490026741817</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.68115725242296</v>
+        <v>82.01994856768152</v>
       </c>
       <c r="C15" t="n">
-        <v>37.67378728637421</v>
+        <v>38.14163347739702</v>
       </c>
       <c r="D15" t="n">
-        <v>1.388896906082086</v>
+        <v>1.428710998857972</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01876630690241</v>
+        <v>12.01098250456374</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562892525171577</v>
+        <v>0.7561938256768007</v>
       </c>
       <c r="G15" t="n">
-        <v>23.54610347247057</v>
+        <v>23.98267760342829</v>
       </c>
       <c r="H15" t="n">
-        <v>36.88525370187892</v>
+        <v>36.73264496448114</v>
       </c>
       <c r="I15" t="n">
-        <v>2.35903978433959</v>
+        <v>2.382527260193577</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726807828232235</v>
+        <v>4.726211410480006</v>
       </c>
       <c r="K15" t="n">
-        <v>18.31884274757702</v>
+        <v>17.98005143231849</v>
       </c>
       <c r="L15" t="n">
-        <v>43.92881093555081</v>
+        <v>43.79897433833043</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92144096950206</v>
+        <v>99.92065924804594</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.07562829778307</v>
+        <v>79.41056134456392</v>
       </c>
       <c r="C16" t="n">
-        <v>35.43217139782392</v>
+        <v>35.90008427332498</v>
       </c>
       <c r="D16" t="n">
-        <v>1.292039529990207</v>
+        <v>1.330198429944922</v>
       </c>
       <c r="E16" t="n">
-        <v>11.5085308579079</v>
+        <v>11.51398307186825</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569164987835525</v>
+        <v>0.7568245685231341</v>
       </c>
       <c r="G16" t="n">
-        <v>21.90407101524181</v>
+        <v>22.32902253811717</v>
       </c>
       <c r="H16" t="n">
-        <v>36.91584535393866</v>
+        <v>36.76328374021766</v>
       </c>
       <c r="I16" t="n">
-        <v>1.967496924523729</v>
+        <v>1.987095442623201</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730728117397202</v>
+        <v>4.73015355326959</v>
       </c>
       <c r="K16" t="n">
-        <v>20.92437170221693</v>
+        <v>20.58943865543608</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57792801706081</v>
+        <v>43.44429575845579</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93447111710167</v>
+        <v>99.93381868721686</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.00962218776407</v>
+        <v>81.10428230140752</v>
       </c>
       <c r="C17" t="n">
-        <v>36.83044743827919</v>
+        <v>37.14252558370765</v>
       </c>
       <c r="D17" t="n">
-        <v>1.29307462656027</v>
+        <v>1.331270872419398</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36499270239199</v>
+        <v>12.29347446742694</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575228901930481</v>
+        <v>0.7574347412573212</v>
       </c>
       <c r="G17" t="n">
-        <v>22.44436333634806</v>
+        <v>22.79029082590957</v>
       </c>
       <c r="H17" t="n">
-        <v>37.46816411523336</v>
+        <v>37.23618932546308</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9469864533308</v>
+        <v>1.961654936072967</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73451806370655</v>
+        <v>4.73396713285826</v>
       </c>
       <c r="K17" t="n">
-        <v>18.99037781223592</v>
+        <v>18.89571769859245</v>
       </c>
       <c r="L17" t="n">
-        <v>44.1143271526438</v>
+        <v>43.89642089536357</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9351524031589</v>
+        <v>99.93466417766368</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.49694693099184</v>
+        <v>78.57228624981572</v>
       </c>
       <c r="C18" t="n">
-        <v>34.61769308390595</v>
+        <v>34.91292692987599</v>
       </c>
       <c r="D18" t="n">
-        <v>1.203908034266332</v>
+        <v>1.239565113657664</v>
       </c>
       <c r="E18" t="n">
-        <v>11.7829406921843</v>
+        <v>11.71926887625292</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580451694145007</v>
+        <v>0.7579603919440864</v>
       </c>
       <c r="G18" t="n">
-        <v>20.89666658799192</v>
+        <v>21.22036170337694</v>
       </c>
       <c r="H18" t="n">
-        <v>37.4939967914953</v>
+        <v>37.26203079724315</v>
       </c>
       <c r="I18" t="n">
-        <v>1.623607346798857</v>
+        <v>1.635846917690422</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737782308840629</v>
+        <v>4.737252449650542</v>
       </c>
       <c r="K18" t="n">
-        <v>21.50305306900817</v>
+        <v>21.42771375018426</v>
       </c>
       <c r="L18" t="n">
-        <v>43.82517089004892</v>
+        <v>43.60486890504881</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94591704296303</v>
+        <v>99.94550958510908</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.49674236990516</v>
+        <v>77.54814667969953</v>
       </c>
       <c r="C19" t="n">
-        <v>33.84734525295262</v>
+        <v>34.12736748928795</v>
       </c>
       <c r="D19" t="n">
-        <v>1.168254262749983</v>
+        <v>1.202592905976064</v>
       </c>
       <c r="E19" t="n">
-        <v>11.66277162873393</v>
+        <v>11.59913027926872</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584927440985891</v>
+        <v>0.7584088438731107</v>
       </c>
       <c r="G19" t="n">
-        <v>20.27781119806538</v>
+        <v>20.58742712710378</v>
       </c>
       <c r="H19" t="n">
-        <v>37.51613447463907</v>
+        <v>37.28407710700813</v>
       </c>
       <c r="I19" t="n">
-        <v>1.372698411002035</v>
+        <v>1.37645514226279</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740579650616181</v>
+        <v>4.740055274206944</v>
       </c>
       <c r="K19" t="n">
-        <v>22.50325763009482</v>
+        <v>22.45185332030045</v>
       </c>
       <c r="L19" t="n">
-        <v>43.60366750351332</v>
+        <v>43.37492448255617</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95427038656075</v>
+        <v>99.95414529214457</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.75840258583476</v>
+        <v>74.92473028188824</v>
       </c>
       <c r="C20" t="n">
-        <v>31.31964260666108</v>
+        <v>31.71531708372468</v>
       </c>
       <c r="D20" t="n">
-        <v>1.07217806782049</v>
+        <v>1.108669835622387</v>
       </c>
       <c r="E20" t="n">
-        <v>10.89438547786477</v>
+        <v>10.88450469415301</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588798106259911</v>
+        <v>0.7587960653560569</v>
       </c>
       <c r="G20" t="n">
-        <v>18.61018198109781</v>
+        <v>18.9795394064534</v>
       </c>
       <c r="H20" t="n">
-        <v>37.53527933792962</v>
+        <v>37.30311327166297</v>
       </c>
       <c r="I20" t="n">
-        <v>1.144499094083644</v>
+        <v>1.147631600165059</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742998816412443</v>
+        <v>4.742475408475358</v>
       </c>
       <c r="K20" t="n">
-        <v>25.24159741416523</v>
+        <v>25.07526971811174</v>
       </c>
       <c r="L20" t="n">
-        <v>43.40062946775694</v>
+        <v>43.17117833310073</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96186948858326</v>
+        <v>99.96176513493715</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.0537811995011</v>
+        <v>81.11735918082812</v>
       </c>
       <c r="C21" t="n">
-        <v>35.32999311814805</v>
+        <v>35.63589034385174</v>
       </c>
       <c r="D21" t="n">
-        <v>1.072850715260142</v>
+        <v>1.109381811932296</v>
       </c>
       <c r="E21" t="n">
-        <v>13.02678294093691</v>
+        <v>12.97517028227424</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593559055741543</v>
+        <v>0.7592833563467809</v>
       </c>
       <c r="G21" t="n">
-        <v>20.49316837221021</v>
+        <v>20.81493989376668</v>
       </c>
       <c r="H21" t="n">
-        <v>39.43013868062002</v>
+        <v>39.15028096873135</v>
       </c>
       <c r="I21" t="n">
-        <v>1.525510175061196</v>
+        <v>1.562781890609371</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745974409838463</v>
+        <v>4.745520977167383</v>
       </c>
       <c r="K21" t="n">
-        <v>18.9462188004989</v>
+        <v>18.88264081917188</v>
       </c>
       <c r="L21" t="n">
-        <v>45.67296962392705</v>
+        <v>45.42940953923235</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94918154257398</v>
+        <v>99.94794070225598</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_89_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.24937863376399</v>
+        <v>45.22885241056667</v>
       </c>
       <c r="M2" t="n">
-        <v>99.16034707666788</v>
+        <v>100.0767003636487</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.90277871229796</v>
+        <v>87.96773114041093</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82539387467031</v>
+        <v>45.8880426045245</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228489189773821</v>
+        <v>2.228608532142231</v>
       </c>
       <c r="E3" t="n">
-        <v>5.640726920586574</v>
+        <v>5.679927201292196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428297299246071</v>
+        <v>0.7428695107140771</v>
       </c>
       <c r="G3" t="n">
-        <v>33.93853535422761</v>
+        <v>33.95962945241379</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17016757653192</v>
+        <v>34.17199749284755</v>
       </c>
       <c r="I3" t="n">
-        <v>6.539344129224647</v>
+        <v>6.5417645090381</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642685812028794</v>
+        <v>4.642934441962982</v>
       </c>
       <c r="K3" t="n">
-        <v>12.09722128770204</v>
+        <v>12.03226885958907</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84263048802675</v>
+        <v>48.84485987343848</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652456503991</v>
+        <v>106.765171337552</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.94956574019136</v>
+        <v>87.08305211750461</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5056104625761</v>
+        <v>42.63493407768906</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182238804785277</v>
+        <v>2.186079462938488</v>
       </c>
       <c r="E4" t="n">
-        <v>6.433802106570004</v>
+        <v>6.482014086750592</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443848423648421</v>
+        <v>0.7444228934861384</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23417011284197</v>
+        <v>33.31156972802295</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24170274878274</v>
+        <v>34.24345310036237</v>
       </c>
       <c r="I4" t="n">
-        <v>5.460861860066278</v>
+        <v>5.462869761655694</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652405264780263</v>
+        <v>4.652643084288365</v>
       </c>
       <c r="K4" t="n">
-        <v>13.05043425980864</v>
+        <v>12.91694788249538</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26230682958126</v>
+        <v>44.26640235900895</v>
       </c>
       <c r="M4" t="n">
-        <v>99.818351551966</v>
+        <v>99.8182843191934</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.77766759028114</v>
+        <v>85.87848042838128</v>
       </c>
       <c r="C5" t="n">
-        <v>42.18115075277218</v>
+        <v>42.2782463934159</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124888996304329</v>
+        <v>2.12711030407231</v>
       </c>
       <c r="E5" t="n">
-        <v>7.024516771547082</v>
+        <v>7.067237704919441</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457035565299261</v>
+        <v>0.7457406093914639</v>
       </c>
       <c r="G5" t="n">
-        <v>32.36076740053787</v>
+        <v>32.41299523396813</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30236360037659</v>
+        <v>34.30406803200734</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558780036673299</v>
+        <v>4.560449735325943</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660647228312038</v>
+        <v>4.66087880869665</v>
       </c>
       <c r="K5" t="n">
-        <v>14.22233240971886</v>
+        <v>14.12151957161872</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4448262302849</v>
+        <v>43.44848765269714</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84830939277595</v>
+        <v>99.84825361773176</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.28551343844909</v>
+        <v>84.42418114190313</v>
       </c>
       <c r="C6" t="n">
-        <v>41.39688646706956</v>
+        <v>41.53218036244624</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051588588848838</v>
+        <v>2.055846343047316</v>
       </c>
       <c r="E6" t="n">
-        <v>7.416314866209291</v>
+        <v>7.464813725322823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468256070227755</v>
+        <v>0.7468612807191147</v>
       </c>
       <c r="G6" t="n">
-        <v>31.24444676442118</v>
+        <v>31.32707203354238</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35397792304767</v>
+        <v>34.35561891307928</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804699645007007</v>
+        <v>3.806085841697747</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667660043892346</v>
+        <v>4.667883004494467</v>
       </c>
       <c r="K6" t="n">
-        <v>15.71448656155091</v>
+        <v>15.57581885809687</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76199419258305</v>
+        <v>42.76532162014228</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87336722120351</v>
+        <v>99.87332084068539</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.68115109091207</v>
+        <v>82.7274377880551</v>
       </c>
       <c r="C7" t="n">
-        <v>40.38324398521604</v>
+        <v>40.42647306235273</v>
       </c>
       <c r="D7" t="n">
-        <v>1.973263393138086</v>
+        <v>1.972971513723479</v>
       </c>
       <c r="E7" t="n">
-        <v>7.662282905026018</v>
+        <v>7.693193254302609</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477814488909371</v>
+        <v>0.7478169812502876</v>
       </c>
       <c r="G7" t="n">
-        <v>30.05160165843888</v>
+        <v>30.06422193933393</v>
       </c>
       <c r="H7" t="n">
-        <v>34.3979466489831</v>
+        <v>34.39958113751324</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17464098086669</v>
+        <v>3.175796829117266</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673634055568357</v>
+        <v>4.673856132814297</v>
       </c>
       <c r="K7" t="n">
-        <v>17.31884890908792</v>
+        <v>17.2725622119449</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19222100444585</v>
+        <v>42.19524011898854</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89431389874981</v>
+        <v>99.89427539328616</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.61450041566268</v>
+        <v>87.46715771359185</v>
       </c>
       <c r="C8" t="n">
-        <v>42.71609136657656</v>
+        <v>42.71308964720073</v>
       </c>
       <c r="D8" t="n">
-        <v>1.977505799910029</v>
+        <v>1.977113622352532</v>
       </c>
       <c r="E8" t="n">
-        <v>9.516744464727742</v>
+        <v>9.50844795035278</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493891375014593</v>
+        <v>0.7493869680186944</v>
       </c>
       <c r="G8" t="n">
-        <v>30.56428918997685</v>
+        <v>30.56781409768342</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47190032506712</v>
+        <v>34.47180052885995</v>
       </c>
       <c r="I8" t="n">
-        <v>5.650989389095344</v>
+        <v>5.508925996207641</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683682109384121</v>
+        <v>4.683668550116839</v>
       </c>
       <c r="K8" t="n">
-        <v>12.38549958433735</v>
+        <v>12.53284228640814</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71044684442368</v>
+        <v>44.57082191167943</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81203779533757</v>
+        <v>99.8167538452883</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.63033520427932</v>
+        <v>85.24613263630188</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60862301810712</v>
+        <v>41.34686617170183</v>
       </c>
       <c r="D9" t="n">
-        <v>1.887674804981699</v>
+        <v>1.876061218857696</v>
       </c>
       <c r="E9" t="n">
-        <v>9.870733934430625</v>
+        <v>9.788965516329474</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507653914925577</v>
+        <v>0.7507346151558674</v>
       </c>
       <c r="G9" t="n">
-        <v>29.17586317001891</v>
+        <v>29.00546024546589</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53520800865765</v>
+        <v>34.5337922971699</v>
       </c>
       <c r="I9" t="n">
-        <v>4.717806197869389</v>
+        <v>4.599027398598874</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692283696828486</v>
+        <v>4.69209134472417</v>
       </c>
       <c r="K9" t="n">
-        <v>14.36966479572066</v>
+        <v>14.75386736369813</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86474025869736</v>
+        <v>43.74624074248316</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84302807252516</v>
+        <v>99.84697427788311</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.43905719194689</v>
+        <v>82.85480394223599</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14901014940652</v>
+        <v>39.66864670710401</v>
       </c>
       <c r="D10" t="n">
-        <v>1.789435012492847</v>
+        <v>1.768479998730493</v>
       </c>
       <c r="E10" t="n">
-        <v>10.01331539520456</v>
+        <v>9.867365367294676</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519464056270792</v>
+        <v>0.7518939326313656</v>
       </c>
       <c r="G10" t="n">
-        <v>27.6574709469826</v>
+        <v>27.34216548077888</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58953465884563</v>
+        <v>34.58712090104282</v>
       </c>
       <c r="I10" t="n">
-        <v>3.937689737624924</v>
+        <v>3.83844118281172</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699665035169245</v>
+        <v>4.699337078946034</v>
       </c>
       <c r="K10" t="n">
-        <v>16.56094280805312</v>
+        <v>17.145196057764</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15899687037729</v>
+        <v>43.0584064740598</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86894982783693</v>
+        <v>99.87224923892781</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.01196086653073</v>
+        <v>80.31670275456881</v>
       </c>
       <c r="C11" t="n">
-        <v>38.33197278733883</v>
+        <v>37.72492042271429</v>
       </c>
       <c r="D11" t="n">
-        <v>1.681641995233472</v>
+        <v>1.655521010087312</v>
       </c>
       <c r="E11" t="n">
-        <v>9.957768296242506</v>
+        <v>9.770927812904862</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529630369957599</v>
+        <v>0.7528934262452071</v>
       </c>
       <c r="G11" t="n">
-        <v>25.99142427732145</v>
+        <v>25.59572596082934</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63629970180494</v>
+        <v>34.63309760727953</v>
       </c>
       <c r="I11" t="n">
-        <v>3.285844577709097</v>
+        <v>3.20295302319</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7060189812235</v>
+        <v>4.705583914032543</v>
       </c>
       <c r="K11" t="n">
-        <v>18.98803913346927</v>
+        <v>19.6832972454312</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57060780870231</v>
+        <v>42.48515896566529</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89061972951042</v>
+        <v>99.89337663381079</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.48416452613336</v>
+        <v>77.71167139822035</v>
       </c>
       <c r="C12" t="n">
-        <v>36.31236856785541</v>
+        <v>35.61489144027243</v>
       </c>
       <c r="D12" t="n">
-        <v>1.570506577429329</v>
+        <v>1.540795827193238</v>
       </c>
       <c r="E12" t="n">
-        <v>9.75658351614141</v>
+        <v>9.539181294307895</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538397177900882</v>
+        <v>0.7537563905372934</v>
       </c>
       <c r="G12" t="n">
-        <v>24.27371753321518</v>
+        <v>23.82197961495368</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67662701834404</v>
+        <v>34.6727939647155</v>
       </c>
       <c r="I12" t="n">
-        <v>2.741391927025259</v>
+        <v>2.672186865654652</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711498236188052</v>
+        <v>4.710977440858082</v>
       </c>
       <c r="K12" t="n">
-        <v>21.51583547386665</v>
+        <v>22.28832860177966</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08052249778603</v>
+        <v>42.00780904063708</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90872653950808</v>
+        <v>99.91102908268917</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.97053115965512</v>
+        <v>75.24476828939963</v>
       </c>
       <c r="C13" t="n">
-        <v>34.22176285685129</v>
+        <v>33.55994708284565</v>
       </c>
       <c r="D13" t="n">
-        <v>1.461083800085499</v>
+        <v>1.433304855525948</v>
       </c>
       <c r="E13" t="n">
-        <v>9.457938560957661</v>
+        <v>9.245200258072622</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545960942756057</v>
+        <v>0.7545006899157514</v>
       </c>
       <c r="G13" t="n">
-        <v>22.58248132502836</v>
+        <v>22.16008016620303</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71142033667785</v>
+        <v>34.70703173612457</v>
       </c>
       <c r="I13" t="n">
-        <v>2.286785453407622</v>
+        <v>2.229021271584265</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716225589222537</v>
+        <v>4.715629311973444</v>
       </c>
       <c r="K13" t="n">
-        <v>24.02946884034487</v>
+        <v>24.75523171060037</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67261852705314</v>
+        <v>41.61059379361912</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92385022424929</v>
+        <v>99.92577258706514</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.93817719546355</v>
+        <v>82.6927009994937</v>
       </c>
       <c r="C14" t="n">
-        <v>38.61882585410319</v>
+        <v>38.24226295607072</v>
       </c>
       <c r="D14" t="n">
-        <v>1.462761051618435</v>
+        <v>1.434950747353227</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89068519303114</v>
+        <v>11.82046865457934</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554623330606757</v>
+        <v>0.7553670977245444</v>
       </c>
       <c r="G14" t="n">
-        <v>24.5542497676985</v>
+        <v>24.27539079034848</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69711219807933</v>
+        <v>36.83675026865502</v>
       </c>
       <c r="I14" t="n">
-        <v>2.856267070346251</v>
+        <v>2.848729080054683</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721639581629224</v>
+        <v>4.7210443607784</v>
       </c>
       <c r="K14" t="n">
-        <v>17.06182280453644</v>
+        <v>17.30729900050632</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22425160877854</v>
+        <v>44.35558932404935</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90490026741817</v>
+        <v>99.90515128062638</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.01994856768152</v>
+        <v>81.88858090737624</v>
       </c>
       <c r="C15" t="n">
-        <v>38.14163347739702</v>
+        <v>37.861436637626</v>
       </c>
       <c r="D15" t="n">
-        <v>1.428710998857972</v>
+        <v>1.403695455718184</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01098250456374</v>
+        <v>11.97533448491428</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561938256768007</v>
+        <v>0.7560977373828524</v>
       </c>
       <c r="G15" t="n">
-        <v>23.98267760342829</v>
+        <v>23.76293097718505</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73264496448114</v>
+        <v>36.88867426510625</v>
       </c>
       <c r="I15" t="n">
-        <v>2.382527260193577</v>
+        <v>2.376237128426812</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726211410480006</v>
+        <v>4.725610858642825</v>
       </c>
       <c r="K15" t="n">
-        <v>17.98005143231849</v>
+        <v>18.11141909262375</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79897433833043</v>
+        <v>43.94801290641541</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92065924804594</v>
+        <v>99.92086863666515</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.41056134456392</v>
+        <v>79.3477687614003</v>
       </c>
       <c r="C16" t="n">
-        <v>35.90008427332498</v>
+        <v>35.68727944372813</v>
       </c>
       <c r="D16" t="n">
-        <v>1.330198429944922</v>
+        <v>1.308759983307573</v>
       </c>
       <c r="E16" t="n">
-        <v>11.51398307186825</v>
+        <v>11.49572004409941</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568245685231341</v>
+        <v>0.7567272318547106</v>
       </c>
       <c r="G16" t="n">
-        <v>22.32902253811717</v>
+        <v>22.15578387915189</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76328374021766</v>
+        <v>36.91938618947258</v>
       </c>
       <c r="I16" t="n">
-        <v>1.987095442623201</v>
+        <v>1.981846234422185</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73015355326959</v>
+        <v>4.729545199091938</v>
       </c>
       <c r="K16" t="n">
-        <v>20.58943865543608</v>
+        <v>20.65223123859971</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44429575845579</v>
+        <v>43.59448273077141</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93381868721686</v>
+        <v>99.93399341309924</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.10428230140752</v>
+        <v>81.30090673161409</v>
       </c>
       <c r="C17" t="n">
-        <v>37.14252558370765</v>
+        <v>37.09037190967703</v>
       </c>
       <c r="D17" t="n">
-        <v>1.331270872419398</v>
+        <v>1.309819852945036</v>
       </c>
       <c r="E17" t="n">
-        <v>12.29347446742694</v>
+        <v>12.35687532489559</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574347412573212</v>
+        <v>0.7573400502684102</v>
       </c>
       <c r="G17" t="n">
-        <v>22.79029082590957</v>
+        <v>22.69637347940004</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23618932546308</v>
+        <v>37.47193175875085</v>
       </c>
       <c r="I17" t="n">
-        <v>1.961654936072967</v>
+        <v>1.975190951176619</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73396713285826</v>
+        <v>4.733375314177561</v>
       </c>
       <c r="K17" t="n">
-        <v>18.89571769859245</v>
+        <v>18.69909326838589</v>
       </c>
       <c r="L17" t="n">
-        <v>43.89642089536357</v>
+        <v>44.14474839920932</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93466417766368</v>
+        <v>99.93421357727225</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.57228624981572</v>
+        <v>78.87882715298974</v>
       </c>
       <c r="C18" t="n">
-        <v>34.91292692987599</v>
+        <v>34.97266120543703</v>
       </c>
       <c r="D18" t="n">
-        <v>1.239565113657664</v>
+        <v>1.223426062005034</v>
       </c>
       <c r="E18" t="n">
-        <v>11.71926887625292</v>
+        <v>11.81635703255172</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579603919440864</v>
+        <v>0.7578672063937862</v>
       </c>
       <c r="G18" t="n">
-        <v>21.22036170337694</v>
+        <v>21.19935406786286</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26203079724315</v>
+        <v>37.49801457102163</v>
       </c>
       <c r="I18" t="n">
-        <v>1.635846917690422</v>
+        <v>1.647138173193555</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737252449650542</v>
+        <v>4.736670039961162</v>
       </c>
       <c r="K18" t="n">
-        <v>21.42771375018426</v>
+        <v>21.12117284701024</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60486890504881</v>
+        <v>43.85129953224227</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94550958510908</v>
+        <v>99.94513358468954</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.54814667969953</v>
+        <v>77.95694642374792</v>
       </c>
       <c r="C19" t="n">
-        <v>34.12736748928795</v>
+        <v>34.29864293444443</v>
       </c>
       <c r="D19" t="n">
-        <v>1.202592905976064</v>
+        <v>1.190969339102232</v>
       </c>
       <c r="E19" t="n">
-        <v>11.59913027926872</v>
+        <v>11.73262781342658</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584088438731107</v>
+        <v>0.758313916987278</v>
       </c>
       <c r="G19" t="n">
-        <v>20.58742712710378</v>
+        <v>20.63694855594221</v>
       </c>
       <c r="H19" t="n">
-        <v>37.28407710700813</v>
+        <v>37.52011707156852</v>
       </c>
       <c r="I19" t="n">
-        <v>1.37645514226279</v>
+        <v>1.378507745550615</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740055274206944</v>
+        <v>4.739461981170486</v>
       </c>
       <c r="K19" t="n">
-        <v>22.45185332030045</v>
+        <v>22.04305357625208</v>
       </c>
       <c r="L19" t="n">
-        <v>43.37492448255617</v>
+        <v>43.61238029968024</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95414529214457</v>
+        <v>99.95407681037675</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.92473028188824</v>
+        <v>75.28062364215478</v>
       </c>
       <c r="C20" t="n">
-        <v>31.71531708372468</v>
+        <v>31.83399625296941</v>
       </c>
       <c r="D20" t="n">
-        <v>1.108669835622387</v>
+        <v>1.096551940719337</v>
       </c>
       <c r="E20" t="n">
-        <v>10.88450469415301</v>
+        <v>10.99404803997529</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587960653560569</v>
+        <v>0.758699833614435</v>
       </c>
       <c r="G20" t="n">
-        <v>18.9795394064534</v>
+        <v>19.00089720748137</v>
       </c>
       <c r="H20" t="n">
-        <v>37.30311327166297</v>
+        <v>37.53921158731778</v>
       </c>
       <c r="I20" t="n">
-        <v>1.147631600165059</v>
+        <v>1.149341072956342</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742475408475358</v>
+        <v>4.741873960090217</v>
       </c>
       <c r="K20" t="n">
-        <v>25.07526971811174</v>
+        <v>24.71937635784523</v>
       </c>
       <c r="L20" t="n">
-        <v>43.17117833310073</v>
+        <v>43.40833550736452</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96176513493715</v>
+        <v>99.96170811817916</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.11735918082812</v>
+        <v>81.56098151594614</v>
       </c>
       <c r="C21" t="n">
-        <v>35.63589034385174</v>
+        <v>35.80393790075435</v>
       </c>
       <c r="D21" t="n">
-        <v>1.109381811932296</v>
+        <v>1.097259575378431</v>
       </c>
       <c r="E21" t="n">
-        <v>12.97517028227424</v>
+        <v>13.11087273894412</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592833563467809</v>
+        <v>0.7591894431606659</v>
       </c>
       <c r="G21" t="n">
-        <v>20.81493989376668</v>
+        <v>20.85972139387513</v>
       </c>
       <c r="H21" t="n">
-        <v>39.15028096873135</v>
+        <v>39.40999904994973</v>
       </c>
       <c r="I21" t="n">
-        <v>1.562781890609371</v>
+        <v>1.57900529488391</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745520977167383</v>
+        <v>4.744934019754161</v>
       </c>
       <c r="K21" t="n">
-        <v>18.88264081917188</v>
+        <v>18.43901848405387</v>
       </c>
       <c r="L21" t="n">
-        <v>45.42940953923235</v>
+        <v>45.70444404928644</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94794070225598</v>
+        <v>99.94740043409466</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_89_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.22885241056667</v>
+        <v>43.51032281874852</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0767003636487</v>
+        <v>95.45901628924253</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96773114041093</v>
+        <v>81.58347885955295</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8880426045245</v>
+        <v>43.33903441510852</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228608532142231</v>
+        <v>2.186227255616227</v>
       </c>
       <c r="E3" t="n">
-        <v>5.679927201292196</v>
+        <v>4.15600939043131</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428695107140771</v>
+        <v>0.7377081087421427</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95962945241379</v>
+        <v>32.88450163656074</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17199749284755</v>
+        <v>33.93457300213856</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5417645090381</v>
+        <v>3.073783786425594</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642934441962982</v>
+        <v>4.610675679638391</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03226885958907</v>
+        <v>18.41652114044703</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84485987343848</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.765171337552</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08305211750461</v>
+        <v>88.75852049383977</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63493407768906</v>
+        <v>42.95117585823897</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186079462938488</v>
+        <v>2.192012654289331</v>
       </c>
       <c r="E4" t="n">
-        <v>6.482014086750592</v>
+        <v>6.554898035911982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444228934861384</v>
+        <v>0.7396603008129767</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31156972802295</v>
+        <v>33.57826627876376</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24345310036237</v>
+        <v>34.02437383739692</v>
       </c>
       <c r="I4" t="n">
-        <v>5.462869761655694</v>
+        <v>7.046432506583685</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652643084288365</v>
+        <v>4.622876880081105</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91694788249538</v>
+        <v>11.24147950616024</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26640235900895</v>
+        <v>45.57308347580001</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8182843191934</v>
+        <v>99.76573884019922</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.87848042838128</v>
+        <v>87.82474284652447</v>
       </c>
       <c r="C5" t="n">
-        <v>42.2782463934159</v>
+        <v>43.10973080393268</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12711030407231</v>
+        <v>2.148440703193112</v>
       </c>
       <c r="E5" t="n">
-        <v>7.067237704919441</v>
+        <v>7.40545960299302</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457406093914639</v>
+        <v>0.7413124574035024</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41299523396813</v>
+        <v>32.91081092747681</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30406803200734</v>
+        <v>34.1003730405611</v>
       </c>
       <c r="I5" t="n">
-        <v>4.560449735325943</v>
+        <v>5.88514325612502</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66087880869665</v>
+        <v>4.63320285877189</v>
       </c>
       <c r="K5" t="n">
-        <v>14.12151957161872</v>
+        <v>12.17525715347556</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44848765269714</v>
+        <v>44.51927780629777</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84825361773176</v>
+        <v>99.804265763706</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.42418114190313</v>
+        <v>86.65092682870095</v>
       </c>
       <c r="C6" t="n">
-        <v>41.53218036244624</v>
+        <v>42.84958868103808</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055846343047316</v>
+        <v>2.0930018488271</v>
       </c>
       <c r="E6" t="n">
-        <v>7.464813725322823</v>
+        <v>8.033293431733702</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468612807191147</v>
+        <v>0.7427136658311523</v>
       </c>
       <c r="G6" t="n">
-        <v>31.32707203354238</v>
+        <v>32.06157284919799</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35561891307928</v>
+        <v>34.164828628233</v>
       </c>
       <c r="I6" t="n">
-        <v>3.806085841697747</v>
+        <v>4.913555993433302</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667883004494467</v>
+        <v>4.641960411444702</v>
       </c>
       <c r="K6" t="n">
-        <v>15.57581885809687</v>
+        <v>13.34907317129906</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76532162014228</v>
+        <v>43.63786194610384</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87332084068539</v>
+        <v>99.83652379844099</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.7274377880551</v>
+        <v>85.21104421739548</v>
       </c>
       <c r="C7" t="n">
-        <v>40.42647306235273</v>
+        <v>42.17313751670579</v>
       </c>
       <c r="D7" t="n">
-        <v>1.972971513723479</v>
+        <v>2.024810427198536</v>
       </c>
       <c r="E7" t="n">
-        <v>7.693193254302609</v>
+        <v>8.455096464915821</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478169812502876</v>
+        <v>0.7439052236743553</v>
       </c>
       <c r="G7" t="n">
-        <v>30.06422193933393</v>
+        <v>31.01698503220214</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39958113751324</v>
+        <v>34.21964028902033</v>
       </c>
       <c r="I7" t="n">
-        <v>3.175796829117266</v>
+        <v>4.101199132419585</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673856132814297</v>
+        <v>4.64940764796472</v>
       </c>
       <c r="K7" t="n">
-        <v>17.2725622119449</v>
+        <v>14.78895578260451</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19524011898854</v>
+        <v>42.90141903420545</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89427539328616</v>
+        <v>99.86351233351574</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.46715771359185</v>
+        <v>83.68105670314554</v>
       </c>
       <c r="C8" t="n">
-        <v>42.71308964720073</v>
+        <v>41.28042062435473</v>
       </c>
       <c r="D8" t="n">
-        <v>1.977113622352532</v>
+        <v>1.952814341428333</v>
       </c>
       <c r="E8" t="n">
-        <v>9.50844795035278</v>
+        <v>8.724846519637582</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493869680186944</v>
+        <v>0.7449193462570902</v>
       </c>
       <c r="G8" t="n">
-        <v>30.56781409768342</v>
+        <v>29.91411560565479</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47180052885995</v>
+        <v>34.26628992782614</v>
       </c>
       <c r="I8" t="n">
-        <v>5.508925996207641</v>
+        <v>3.422325048234792</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683668550116839</v>
+        <v>4.655745914106814</v>
       </c>
       <c r="K8" t="n">
-        <v>12.53284228640814</v>
+        <v>16.31894329685446</v>
       </c>
       <c r="L8" t="n">
-        <v>44.57082191167943</v>
+        <v>42.28671388066805</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8167538452883</v>
+        <v>99.88607780187724</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.24613263630188</v>
+        <v>81.94086142477896</v>
       </c>
       <c r="C9" t="n">
-        <v>41.34686617170183</v>
+        <v>40.07182345797715</v>
       </c>
       <c r="D9" t="n">
-        <v>1.876061218857696</v>
+        <v>1.871266919126137</v>
       </c>
       <c r="E9" t="n">
-        <v>9.788965516329474</v>
+        <v>8.836381346916516</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507346151558674</v>
+        <v>0.7457845763727589</v>
       </c>
       <c r="G9" t="n">
-        <v>29.00546024546589</v>
+        <v>28.66493437713781</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5337922971699</v>
+        <v>34.30609051314689</v>
       </c>
       <c r="I9" t="n">
-        <v>4.599027398598874</v>
+        <v>2.855250089749087</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69209134472417</v>
+        <v>4.661153602329742</v>
       </c>
       <c r="K9" t="n">
-        <v>14.75386736369813</v>
+        <v>18.05913857522105</v>
       </c>
       <c r="L9" t="n">
-        <v>43.74624074248316</v>
+        <v>41.77397338212862</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84697427788311</v>
+        <v>99.9049354153268</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.85480394223599</v>
+        <v>86.47697515271457</v>
       </c>
       <c r="C10" t="n">
-        <v>39.66864670710401</v>
+        <v>43.14325648651013</v>
       </c>
       <c r="D10" t="n">
-        <v>1.768479998730493</v>
+        <v>1.873436381492926</v>
       </c>
       <c r="E10" t="n">
-        <v>9.867365367294676</v>
+        <v>10.61146769198105</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7518939326313656</v>
+        <v>0.7466492053338306</v>
       </c>
       <c r="G10" t="n">
-        <v>27.34216548077888</v>
+        <v>29.96172155108858</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58712090104282</v>
+        <v>35.60941778878875</v>
       </c>
       <c r="I10" t="n">
-        <v>3.83844118281172</v>
+        <v>3.007725000692986</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699337078946034</v>
+        <v>4.666557533336441</v>
       </c>
       <c r="K10" t="n">
-        <v>17.145196057764</v>
+        <v>13.52302484728543</v>
       </c>
       <c r="L10" t="n">
-        <v>43.0584064740598</v>
+        <v>43.23357726559919</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87224923892781</v>
+        <v>99.89985859939475</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.31670275456881</v>
+        <v>86.27832832223724</v>
       </c>
       <c r="C11" t="n">
-        <v>37.72492042271429</v>
+        <v>43.31701588248909</v>
       </c>
       <c r="D11" t="n">
-        <v>1.655521010087312</v>
+        <v>1.856866697255839</v>
       </c>
       <c r="E11" t="n">
-        <v>9.770927812904862</v>
+        <v>11.00018015223711</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7528934262452071</v>
+        <v>0.7473832645652698</v>
       </c>
       <c r="G11" t="n">
-        <v>25.59572596082934</v>
+        <v>29.75517237424226</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63309760727953</v>
+        <v>35.70287524921612</v>
       </c>
       <c r="I11" t="n">
-        <v>3.20295302319</v>
+        <v>2.544705181187715</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705583914032543</v>
+        <v>4.671145403532936</v>
       </c>
       <c r="K11" t="n">
-        <v>19.6832972454312</v>
+        <v>13.72167167776274</v>
       </c>
       <c r="L11" t="n">
-        <v>42.48515896566529</v>
+        <v>42.87657224501699</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89337663381079</v>
+        <v>99.91525980526882</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.71167139822035</v>
+        <v>84.52497600983767</v>
       </c>
       <c r="C12" t="n">
-        <v>35.61489144027243</v>
+        <v>41.95968145106585</v>
       </c>
       <c r="D12" t="n">
-        <v>1.540795827193238</v>
+        <v>1.781952960926141</v>
       </c>
       <c r="E12" t="n">
-        <v>9.539181294307895</v>
+        <v>10.9101141584965</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537563905372934</v>
+        <v>0.7480088067869833</v>
       </c>
       <c r="G12" t="n">
-        <v>23.82197961495368</v>
+        <v>28.55472479177286</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6727939647155</v>
+        <v>35.7327577164372</v>
       </c>
       <c r="I12" t="n">
-        <v>2.672186865654652</v>
+        <v>2.122362532999343</v>
       </c>
       <c r="J12" t="n">
-        <v>4.710977440858082</v>
+        <v>4.675055042418646</v>
       </c>
       <c r="K12" t="n">
-        <v>22.28832860177966</v>
+        <v>15.47502399016233</v>
       </c>
       <c r="L12" t="n">
-        <v>42.00780904063708</v>
+        <v>42.49460830373881</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91102908268917</v>
+        <v>99.92931374496699</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.24476828939963</v>
+        <v>85.70555707662558</v>
       </c>
       <c r="C13" t="n">
-        <v>33.55994708284565</v>
+        <v>42.94280612509264</v>
       </c>
       <c r="D13" t="n">
-        <v>1.433304855525948</v>
+        <v>1.783326214861661</v>
       </c>
       <c r="E13" t="n">
-        <v>9.245200258072622</v>
+        <v>11.55801147316448</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545006899157514</v>
+        <v>0.7485852563680037</v>
       </c>
       <c r="G13" t="n">
-        <v>22.16008016620303</v>
+        <v>28.88597685870608</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70703173612457</v>
+        <v>36.06954150175987</v>
       </c>
       <c r="I13" t="n">
-        <v>2.229021271584265</v>
+        <v>1.981457919465454</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715629311973444</v>
+        <v>4.678657852300023</v>
       </c>
       <c r="K13" t="n">
-        <v>24.75523171060037</v>
+        <v>14.29444292337441</v>
       </c>
       <c r="L13" t="n">
-        <v>41.61059379361912</v>
+        <v>42.69675321507251</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92577258706514</v>
+        <v>99.93400226353957</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.6927009994937</v>
+        <v>83.86664545180088</v>
       </c>
       <c r="C14" t="n">
-        <v>38.24226295607072</v>
+        <v>41.41219066709018</v>
       </c>
       <c r="D14" t="n">
-        <v>1.434950747353227</v>
+        <v>1.706786211103019</v>
       </c>
       <c r="E14" t="n">
-        <v>11.82046865457934</v>
+        <v>11.33732715593308</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553670977245444</v>
+        <v>0.7490768649602874</v>
       </c>
       <c r="G14" t="n">
-        <v>24.27539079034848</v>
+        <v>27.64619652075545</v>
       </c>
       <c r="H14" t="n">
-        <v>36.83675026865502</v>
+        <v>36.09322897940007</v>
       </c>
       <c r="I14" t="n">
-        <v>2.848729080054683</v>
+        <v>1.652299313647197</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7210443607784</v>
+        <v>4.681730406001797</v>
       </c>
       <c r="K14" t="n">
-        <v>17.30729900050632</v>
+        <v>16.13335454819911</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35558932404935</v>
+        <v>42.39941428694777</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90515128062638</v>
+        <v>99.94495950223705</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.88858090737624</v>
+        <v>83.07477757103247</v>
       </c>
       <c r="C15" t="n">
-        <v>37.861436637626</v>
+        <v>40.85625892253082</v>
       </c>
       <c r="D15" t="n">
-        <v>1.403695455718184</v>
+        <v>1.673498201756543</v>
       </c>
       <c r="E15" t="n">
-        <v>11.97533448491428</v>
+        <v>11.34917428202156</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560977373828524</v>
+        <v>0.7494969852218221</v>
       </c>
       <c r="G15" t="n">
-        <v>23.76293097718505</v>
+        <v>27.10700371371803</v>
       </c>
       <c r="H15" t="n">
-        <v>36.88867426510625</v>
+        <v>36.11347189105275</v>
       </c>
       <c r="I15" t="n">
-        <v>2.376237128426812</v>
+        <v>1.397776339625373</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725610858642825</v>
+        <v>4.684356157636389</v>
       </c>
       <c r="K15" t="n">
-        <v>18.11141909262375</v>
+        <v>16.92522242896754</v>
       </c>
       <c r="L15" t="n">
-        <v>43.94801290641541</v>
+        <v>42.17195222065972</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92086863666515</v>
+        <v>99.95343357215808</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.3477687614003</v>
+        <v>80.84081067001884</v>
       </c>
       <c r="C16" t="n">
-        <v>35.68727944372813</v>
+        <v>38.83934188443008</v>
       </c>
       <c r="D16" t="n">
-        <v>1.308759983307573</v>
+        <v>1.581096118960696</v>
       </c>
       <c r="E16" t="n">
-        <v>11.49572004409941</v>
+        <v>10.91675932978249</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567272318547106</v>
+        <v>0.7498571349175979</v>
       </c>
       <c r="G16" t="n">
-        <v>22.15578387915189</v>
+        <v>25.6102924541103</v>
       </c>
       <c r="H16" t="n">
-        <v>36.91938618947258</v>
+        <v>36.13082520423669</v>
       </c>
       <c r="I16" t="n">
-        <v>1.981846234422185</v>
+        <v>1.165373334776082</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729545199091938</v>
+        <v>4.686607093234987</v>
       </c>
       <c r="K16" t="n">
-        <v>20.65223123859971</v>
+        <v>19.15918932998116</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59448273077141</v>
+        <v>41.96264166504362</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93399341309924</v>
+        <v>99.96117287945486</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.30090673161409</v>
+        <v>85.30401244811159</v>
       </c>
       <c r="C17" t="n">
-        <v>37.09037190967703</v>
+        <v>41.74761053525894</v>
       </c>
       <c r="D17" t="n">
-        <v>1.309819852945036</v>
+        <v>1.58193822246907</v>
       </c>
       <c r="E17" t="n">
-        <v>12.35687532489559</v>
+        <v>12.48172981084778</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573400502684102</v>
+        <v>0.7502565143838558</v>
       </c>
       <c r="G17" t="n">
-        <v>22.69637347940004</v>
+        <v>26.95592107426572</v>
       </c>
       <c r="H17" t="n">
-        <v>37.47193175875085</v>
+        <v>37.48205713808861</v>
       </c>
       <c r="I17" t="n">
-        <v>1.975190951176619</v>
+        <v>1.363006473157461</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733375314177561</v>
+        <v>4.6891032148991</v>
       </c>
       <c r="K17" t="n">
-        <v>18.69909326838589</v>
+        <v>14.6959875518884</v>
       </c>
       <c r="L17" t="n">
-        <v>44.14474839920932</v>
+        <v>43.51099254911102</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93421357727225</v>
+        <v>99.95459063625836</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.87882715298974</v>
+        <v>86.91768169715095</v>
       </c>
       <c r="C18" t="n">
-        <v>34.97266120543703</v>
+        <v>42.49934443367941</v>
       </c>
       <c r="D18" t="n">
-        <v>1.223426062005034</v>
+        <v>1.583258664407038</v>
       </c>
       <c r="E18" t="n">
-        <v>11.81635703255172</v>
+        <v>13.09980358595836</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578672063937862</v>
+        <v>0.7508827525970522</v>
       </c>
       <c r="G18" t="n">
-        <v>21.19935406786286</v>
+        <v>27.10087358257025</v>
       </c>
       <c r="H18" t="n">
-        <v>37.49801457102163</v>
+        <v>37.51334336625067</v>
       </c>
       <c r="I18" t="n">
-        <v>1.647138173193555</v>
+        <v>2.176502541636032</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736670039961162</v>
+        <v>4.693017203731577</v>
       </c>
       <c r="K18" t="n">
-        <v>21.12117284701024</v>
+        <v>13.08231830284904</v>
       </c>
       <c r="L18" t="n">
-        <v>43.85129953224227</v>
+        <v>44.345847685714</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94513358468954</v>
+        <v>99.92751042224245</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.95694642374792</v>
+        <v>84.45991558947723</v>
       </c>
       <c r="C19" t="n">
-        <v>34.29864293444443</v>
+        <v>40.37934449753064</v>
       </c>
       <c r="D19" t="n">
-        <v>1.190969339102232</v>
+        <v>1.491197497902862</v>
       </c>
       <c r="E19" t="n">
-        <v>11.73262781342658</v>
+        <v>12.64060262727397</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758313916987278</v>
+        <v>0.7514206372503152</v>
       </c>
       <c r="G19" t="n">
-        <v>20.63694855594221</v>
+        <v>25.52504892966806</v>
       </c>
       <c r="H19" t="n">
-        <v>37.52011707156852</v>
+        <v>37.54021553986166</v>
       </c>
       <c r="I19" t="n">
-        <v>1.378507745550615</v>
+        <v>1.815051374705903</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739461981170486</v>
+        <v>4.696378982814471</v>
       </c>
       <c r="K19" t="n">
-        <v>22.04305357625208</v>
+        <v>15.54008441052276</v>
       </c>
       <c r="L19" t="n">
-        <v>43.61238029968024</v>
+        <v>44.02011268801227</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95407681037675</v>
+        <v>99.93954159606567</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.28062364215478</v>
+        <v>81.84917355452778</v>
       </c>
       <c r="C20" t="n">
-        <v>31.83399625296941</v>
+        <v>38.0496181258549</v>
       </c>
       <c r="D20" t="n">
-        <v>1.096551940719337</v>
+        <v>1.393885632373093</v>
       </c>
       <c r="E20" t="n">
-        <v>10.99404803997529</v>
+        <v>12.06795397055455</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758699833614435</v>
+        <v>0.75188378850384</v>
       </c>
       <c r="G20" t="n">
-        <v>19.00089720748137</v>
+        <v>23.85934728211443</v>
       </c>
       <c r="H20" t="n">
-        <v>37.53921158731778</v>
+        <v>37.5633541083584</v>
       </c>
       <c r="I20" t="n">
-        <v>1.149341072956342</v>
+        <v>1.513475094474461</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741873960090217</v>
+        <v>4.699273678149001</v>
       </c>
       <c r="K20" t="n">
-        <v>24.71937635784523</v>
+        <v>18.15082644547222</v>
       </c>
       <c r="L20" t="n">
-        <v>43.40833550736452</v>
+        <v>43.74913733493106</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96170811817916</v>
+        <v>99.94958190625817</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.56098151594614</v>
+        <v>79.17036695124291</v>
       </c>
       <c r="C21" t="n">
-        <v>35.80393790075435</v>
+        <v>35.6044689444936</v>
       </c>
       <c r="D21" t="n">
-        <v>1.097259575378431</v>
+        <v>1.294523979374485</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11087273894412</v>
+        <v>11.41801927888468</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591894431606659</v>
+        <v>0.7522832652657953</v>
       </c>
       <c r="G21" t="n">
-        <v>20.85972139387513</v>
+        <v>22.15855911817977</v>
       </c>
       <c r="H21" t="n">
-        <v>39.40999904994973</v>
+        <v>37.58331156361521</v>
       </c>
       <c r="I21" t="n">
-        <v>1.57900529488391</v>
+        <v>1.26189933801174</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744934019754161</v>
+        <v>4.701770407911221</v>
       </c>
       <c r="K21" t="n">
-        <v>18.43901848405387</v>
+        <v>20.82963304875711</v>
       </c>
       <c r="L21" t="n">
-        <v>45.70444404928644</v>
+        <v>43.52385703190279</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94740043409466</v>
+        <v>99.95795902515349</v>
       </c>
     </row>
   </sheetData>
